--- a/TestData/TMTT0046328_VerifyTheFunctionalityOfTheRemovalOfTheMinimumFee1.xlsx
+++ b/TestData/TMTT0046328_VerifyTheFunctionalityOfTheRemovalOfTheMinimumFee1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E096448-3549-447B-B4EA-98F12B4215FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403AE457-A550-4DE2-B354-54B960E72302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
   <si>
     <t>Client</t>
   </si>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>Brian Miller</t>
-  </si>
-  <si>
-    <t>Buyside</t>
-  </si>
-  <si>
-    <t>Buyside &amp; Financing Advisory</t>
   </si>
   <si>
     <t>Equity Capital Markets</t>
@@ -544,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -663,10 +657,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -739,16 +733,6 @@
       </c>
       <c r="AB2" s="3" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
